--- a/WorkBot/main/data/order_archive/Performance Food/Performance Food_Collegetown_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/Performance Food/Performance Food_Collegetown_20260515.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1067,111 +1067,6 @@
         <v>33.98</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>TN330</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Natalie's - Honey Tangerine</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>14.57</v>
-      </c>
-      <c r="E34" t="n">
-        <v>14.57</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TN374</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Natalie's - Lemonade</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" t="n">
-        <v>10.39</v>
-      </c>
-      <c r="E35" t="n">
-        <v>20.78</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>AH252</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Natalie's - Orange Juice</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>4</v>
-      </c>
-      <c r="D36" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E36" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TN454</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Natalie's - Orange Mango</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="E37" t="n">
-        <v>26.76</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>TN362</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Natalie's - Orange Pineapple</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="E38" t="n">
-        <v>13.38</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
